--- a/artfynd/A 49213-2024 artfynd.xlsx
+++ b/artfynd/A 49213-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597809</v>
+        <v>121597811</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456010</v>
+        <v>455994</v>
       </c>
       <c r="R2" t="n">
-        <v>7089636</v>
+        <v>7089624</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597823</v>
+        <v>121597803</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455862</v>
+        <v>456311</v>
       </c>
       <c r="R3" t="n">
-        <v>7089621</v>
+        <v>7089646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121597821</v>
+        <v>121597809</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455920</v>
+        <v>456010</v>
       </c>
       <c r="R4" t="n">
-        <v>7089644</v>
+        <v>7089636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121597838</v>
+        <v>121597814</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456161</v>
+        <v>455985</v>
       </c>
       <c r="R5" t="n">
-        <v>7090000</v>
+        <v>7089602</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121597843</v>
+        <v>121597827</v>
       </c>
       <c r="B6" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,20 +1115,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1136,33 +1136,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455872</v>
+        <v>455876</v>
       </c>
       <c r="R6" t="n">
-        <v>7089681</v>
+        <v>7089661</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121597818</v>
+        <v>121597830</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1261,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455942</v>
+        <v>455863</v>
       </c>
       <c r="R7" t="n">
-        <v>7089594</v>
+        <v>7089690</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597814</v>
+        <v>121597816</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1368,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455985</v>
+        <v>455928</v>
       </c>
       <c r="R8" t="n">
-        <v>7089602</v>
+        <v>7089592</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121597825</v>
+        <v>121597813</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1475,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455860</v>
+        <v>455988</v>
       </c>
       <c r="R9" t="n">
-        <v>7089638</v>
+        <v>7089586</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121597807</v>
+        <v>121597828</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1582,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456131</v>
+        <v>455870</v>
       </c>
       <c r="R10" t="n">
-        <v>7089685</v>
+        <v>7089664</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121597803</v>
+        <v>121597837</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1689,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456311</v>
+        <v>456058</v>
       </c>
       <c r="R11" t="n">
-        <v>7089646</v>
+        <v>7089872</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121597828</v>
+        <v>121597802</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1796,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455870</v>
+        <v>456310</v>
       </c>
       <c r="R12" t="n">
-        <v>7089664</v>
+        <v>7089654</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121597831</v>
+        <v>121597807</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1903,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455932</v>
+        <v>456131</v>
       </c>
       <c r="R13" t="n">
-        <v>7089722</v>
+        <v>7089685</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121597826</v>
+        <v>121597815</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2010,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455858</v>
+        <v>455981</v>
       </c>
       <c r="R14" t="n">
-        <v>7089658</v>
+        <v>7089604</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121597816</v>
+        <v>121597831</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2117,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455928</v>
+        <v>455932</v>
       </c>
       <c r="R15" t="n">
-        <v>7089592</v>
+        <v>7089722</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597837</v>
+        <v>121597832</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2224,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456058</v>
+        <v>455959</v>
       </c>
       <c r="R16" t="n">
-        <v>7089872</v>
+        <v>7089716</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121597824</v>
+        <v>121597810</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2331,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455866</v>
+        <v>456012</v>
       </c>
       <c r="R17" t="n">
-        <v>7089627</v>
+        <v>7089631</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121597839</v>
+        <v>121597826</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2438,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456158</v>
+        <v>455858</v>
       </c>
       <c r="R18" t="n">
-        <v>7090028</v>
+        <v>7089658</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2505,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121597817</v>
+        <v>121597824</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2545,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455940</v>
+        <v>455866</v>
       </c>
       <c r="R19" t="n">
-        <v>7089592</v>
+        <v>7089627</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121597830</v>
+        <v>121597833</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2652,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455863</v>
+        <v>456021</v>
       </c>
       <c r="R20" t="n">
-        <v>7089690</v>
+        <v>7089738</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2719,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121597832</v>
+        <v>121597819</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2759,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455959</v>
+        <v>455921</v>
       </c>
       <c r="R21" t="n">
-        <v>7089716</v>
+        <v>7089667</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121597808</v>
+        <v>121597834</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2866,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456004</v>
+        <v>456027</v>
       </c>
       <c r="R22" t="n">
-        <v>7089704</v>
+        <v>7089731</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2895,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2933,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121597805</v>
+        <v>121597817</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2973,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456204</v>
+        <v>455940</v>
       </c>
       <c r="R23" t="n">
-        <v>7089607</v>
+        <v>7089592</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3040,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121597833</v>
+        <v>121597843</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3052,20 +3041,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3073,17 +3062,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456021</v>
+        <v>455872</v>
       </c>
       <c r="R24" t="n">
-        <v>7089738</v>
+        <v>7089681</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,11 +3121,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,7 +3254,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121597827</v>
+        <v>121597838</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455876</v>
+        <v>456161</v>
       </c>
       <c r="R26" t="n">
-        <v>7089661</v>
+        <v>7090000</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3361,7 +3361,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121597811</v>
+        <v>121597820</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455994</v>
+        <v>455932</v>
       </c>
       <c r="R27" t="n">
-        <v>7089624</v>
+        <v>7089647</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,7 +3468,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121597812</v>
+        <v>121597821</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456010</v>
+        <v>455920</v>
       </c>
       <c r="R28" t="n">
-        <v>7089564</v>
+        <v>7089644</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597810</v>
+        <v>121597825</v>
       </c>
       <c r="B29" t="n">
         <v>57356</v>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456012</v>
+        <v>455860</v>
       </c>
       <c r="R29" t="n">
-        <v>7089631</v>
+        <v>7089638</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121597822</v>
+        <v>121597818</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455878</v>
+        <v>455942</v>
       </c>
       <c r="R30" t="n">
-        <v>7089626</v>
+        <v>7089594</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3789,7 +3789,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121597835</v>
+        <v>121597829</v>
       </c>
       <c r="B31" t="n">
         <v>57356</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456030</v>
+        <v>455874</v>
       </c>
       <c r="R31" t="n">
-        <v>7089739</v>
+        <v>7089674</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3896,7 +3896,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121597802</v>
+        <v>121597805</v>
       </c>
       <c r="B32" t="n">
         <v>57356</v>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456310</v>
+        <v>456204</v>
       </c>
       <c r="R32" t="n">
-        <v>7089654</v>
+        <v>7089607</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4003,7 +4003,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597819</v>
+        <v>121597839</v>
       </c>
       <c r="B33" t="n">
         <v>57356</v>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455921</v>
+        <v>456158</v>
       </c>
       <c r="R33" t="n">
-        <v>7089667</v>
+        <v>7090028</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597820</v>
+        <v>121597808</v>
       </c>
       <c r="B34" t="n">
         <v>57356</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455932</v>
+        <v>456004</v>
       </c>
       <c r="R34" t="n">
-        <v>7089647</v>
+        <v>7089704</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597815</v>
+        <v>121597835</v>
       </c>
       <c r="B35" t="n">
         <v>57356</v>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455981</v>
+        <v>456030</v>
       </c>
       <c r="R35" t="n">
-        <v>7089604</v>
+        <v>7089739</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597813</v>
+        <v>121597822</v>
       </c>
       <c r="B36" t="n">
         <v>57356</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455988</v>
+        <v>455878</v>
       </c>
       <c r="R36" t="n">
-        <v>7089586</v>
+        <v>7089626</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4431,7 +4431,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597829</v>
+        <v>121597812</v>
       </c>
       <c r="B37" t="n">
         <v>57356</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455874</v>
+        <v>456010</v>
       </c>
       <c r="R37" t="n">
-        <v>7089674</v>
+        <v>7089564</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4538,7 +4538,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121597834</v>
+        <v>121597823</v>
       </c>
       <c r="B38" t="n">
         <v>57356</v>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456027</v>
+        <v>455862</v>
       </c>
       <c r="R38" t="n">
-        <v>7089731</v>
+        <v>7089621</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 49213-2024 artfynd.xlsx
+++ b/artfynd/A 49213-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597811</v>
+        <v>121597828</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455994</v>
+        <v>455870</v>
       </c>
       <c r="R2" t="n">
-        <v>7089624</v>
+        <v>7089664</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597803</v>
+        <v>121597835</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456311</v>
+        <v>456030</v>
       </c>
       <c r="R3" t="n">
-        <v>7089646</v>
+        <v>7089739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121597809</v>
+        <v>121597832</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456010</v>
+        <v>455959</v>
       </c>
       <c r="R4" t="n">
-        <v>7089636</v>
+        <v>7089716</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121597814</v>
+        <v>121597821</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455985</v>
+        <v>455920</v>
       </c>
       <c r="R5" t="n">
-        <v>7089602</v>
+        <v>7089644</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121597827</v>
+        <v>121597822</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455876</v>
+        <v>455878</v>
       </c>
       <c r="R6" t="n">
-        <v>7089661</v>
+        <v>7089626</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121597830</v>
+        <v>121597837</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455863</v>
+        <v>456058</v>
       </c>
       <c r="R7" t="n">
-        <v>7089690</v>
+        <v>7089872</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597816</v>
+        <v>121597810</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455928</v>
+        <v>456012</v>
       </c>
       <c r="R8" t="n">
-        <v>7089592</v>
+        <v>7089631</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121597813</v>
+        <v>121597807</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455988</v>
+        <v>456131</v>
       </c>
       <c r="R9" t="n">
-        <v>7089586</v>
+        <v>7089685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121597828</v>
+        <v>121597831</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455870</v>
+        <v>455932</v>
       </c>
       <c r="R10" t="n">
-        <v>7089664</v>
+        <v>7089722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121597837</v>
+        <v>121597843</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,20 +1650,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1671,17 +1671,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456058</v>
+        <v>455872</v>
       </c>
       <c r="R11" t="n">
-        <v>7089872</v>
+        <v>7089681</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,11 +1730,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121597802</v>
+        <v>121597808</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1785,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456310</v>
+        <v>456004</v>
       </c>
       <c r="R12" t="n">
-        <v>7089654</v>
+        <v>7089704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121597807</v>
+        <v>121597823</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1892,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456131</v>
+        <v>455862</v>
       </c>
       <c r="R13" t="n">
-        <v>7089685</v>
+        <v>7089621</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1943,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1970,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121597815</v>
+        <v>121597833</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -1999,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455981</v>
+        <v>456021</v>
       </c>
       <c r="R14" t="n">
-        <v>7089604</v>
+        <v>7089738</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2077,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121597831</v>
+        <v>121597829</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2106,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455932</v>
+        <v>455874</v>
       </c>
       <c r="R15" t="n">
-        <v>7089722</v>
+        <v>7089674</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2157,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2184,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597832</v>
+        <v>121597819</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2213,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455959</v>
+        <v>455921</v>
       </c>
       <c r="R16" t="n">
-        <v>7089716</v>
+        <v>7089667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121597810</v>
+        <v>121597818</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2320,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456012</v>
+        <v>455942</v>
       </c>
       <c r="R17" t="n">
-        <v>7089631</v>
+        <v>7089594</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2371,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2398,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121597826</v>
+        <v>121597834</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2427,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455858</v>
+        <v>456027</v>
       </c>
       <c r="R18" t="n">
-        <v>7089658</v>
+        <v>7089731</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,7 +2505,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121597824</v>
+        <v>121597825</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2534,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455866</v>
+        <v>455860</v>
       </c>
       <c r="R19" t="n">
-        <v>7089627</v>
+        <v>7089638</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,7 +2612,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121597833</v>
+        <v>121597809</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2641,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456021</v>
+        <v>456010</v>
       </c>
       <c r="R20" t="n">
-        <v>7089738</v>
+        <v>7089636</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,7 +2719,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121597819</v>
+        <v>121597812</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2748,10 +2759,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455921</v>
+        <v>456010</v>
       </c>
       <c r="R21" t="n">
-        <v>7089667</v>
+        <v>7089564</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2799,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2826,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121597834</v>
+        <v>121597814</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2855,10 +2866,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456027</v>
+        <v>455985</v>
       </c>
       <c r="R22" t="n">
-        <v>7089731</v>
+        <v>7089602</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2906,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2933,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121597817</v>
+        <v>121597813</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2962,10 +2973,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455940</v>
+        <v>455988</v>
       </c>
       <c r="R23" t="n">
-        <v>7089592</v>
+        <v>7089586</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3013,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121597843</v>
+        <v>121597830</v>
       </c>
       <c r="B24" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3041,20 +3052,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3062,33 +3073,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455872</v>
+        <v>455863</v>
       </c>
       <c r="R24" t="n">
-        <v>7089681</v>
+        <v>7089690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,6 +3116,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3147,7 +3147,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121597836</v>
+        <v>121597820</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456036</v>
+        <v>455932</v>
       </c>
       <c r="R25" t="n">
-        <v>7089837</v>
+        <v>7089647</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,7 +3254,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121597838</v>
+        <v>121597824</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456161</v>
+        <v>455866</v>
       </c>
       <c r="R26" t="n">
-        <v>7090000</v>
+        <v>7089627</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121597820</v>
+        <v>121597815</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455932</v>
+        <v>455981</v>
       </c>
       <c r="R27" t="n">
-        <v>7089647</v>
+        <v>7089604</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121597821</v>
+        <v>121597827</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455920</v>
+        <v>455876</v>
       </c>
       <c r="R28" t="n">
-        <v>7089644</v>
+        <v>7089661</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3575,7 +3575,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597825</v>
+        <v>121597817</v>
       </c>
       <c r="B29" t="n">
         <v>57356</v>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455860</v>
+        <v>455940</v>
       </c>
       <c r="R29" t="n">
-        <v>7089638</v>
+        <v>7089592</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121597818</v>
+        <v>121597805</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455942</v>
+        <v>456204</v>
       </c>
       <c r="R30" t="n">
-        <v>7089594</v>
+        <v>7089607</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3789,7 +3789,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121597829</v>
+        <v>121597811</v>
       </c>
       <c r="B31" t="n">
         <v>57356</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455874</v>
+        <v>455994</v>
       </c>
       <c r="R31" t="n">
-        <v>7089674</v>
+        <v>7089624</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3896,7 +3896,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121597805</v>
+        <v>121597802</v>
       </c>
       <c r="B32" t="n">
         <v>57356</v>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456204</v>
+        <v>456310</v>
       </c>
       <c r="R32" t="n">
-        <v>7089607</v>
+        <v>7089654</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4003,7 +4003,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597839</v>
+        <v>121597826</v>
       </c>
       <c r="B33" t="n">
         <v>57356</v>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456158</v>
+        <v>455858</v>
       </c>
       <c r="R33" t="n">
-        <v>7090028</v>
+        <v>7089658</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597808</v>
+        <v>121597839</v>
       </c>
       <c r="B34" t="n">
         <v>57356</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456004</v>
+        <v>456158</v>
       </c>
       <c r="R34" t="n">
-        <v>7089704</v>
+        <v>7090028</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4217,7 +4217,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597835</v>
+        <v>121597816</v>
       </c>
       <c r="B35" t="n">
         <v>57356</v>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456030</v>
+        <v>455928</v>
       </c>
       <c r="R35" t="n">
-        <v>7089739</v>
+        <v>7089592</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,7 +4324,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597822</v>
+        <v>121597836</v>
       </c>
       <c r="B36" t="n">
         <v>57356</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455878</v>
+        <v>456036</v>
       </c>
       <c r="R36" t="n">
-        <v>7089626</v>
+        <v>7089837</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4431,7 +4431,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597812</v>
+        <v>121597803</v>
       </c>
       <c r="B37" t="n">
         <v>57356</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456010</v>
+        <v>456311</v>
       </c>
       <c r="R37" t="n">
-        <v>7089564</v>
+        <v>7089646</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4538,7 +4538,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121597823</v>
+        <v>121597838</v>
       </c>
       <c r="B38" t="n">
         <v>57356</v>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455862</v>
+        <v>456161</v>
       </c>
       <c r="R38" t="n">
-        <v>7089621</v>
+        <v>7090000</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 49213-2024 artfynd.xlsx
+++ b/artfynd/A 49213-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597828</v>
+        <v>121597826</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455870</v>
+        <v>455858</v>
       </c>
       <c r="R2" t="n">
-        <v>7089664</v>
+        <v>7089658</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597835</v>
+        <v>121597837</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456030</v>
+        <v>456058</v>
       </c>
       <c r="R3" t="n">
-        <v>7089739</v>
+        <v>7089872</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121597832</v>
+        <v>121597827</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455959</v>
+        <v>455876</v>
       </c>
       <c r="R4" t="n">
-        <v>7089716</v>
+        <v>7089661</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121597821</v>
+        <v>121597829</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455920</v>
+        <v>455874</v>
       </c>
       <c r="R5" t="n">
-        <v>7089644</v>
+        <v>7089674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121597822</v>
+        <v>121597809</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455878</v>
+        <v>456010</v>
       </c>
       <c r="R6" t="n">
-        <v>7089626</v>
+        <v>7089636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121597837</v>
+        <v>121597824</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456058</v>
+        <v>455866</v>
       </c>
       <c r="R7" t="n">
-        <v>7089872</v>
+        <v>7089627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597810</v>
+        <v>121597807</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456012</v>
+        <v>456131</v>
       </c>
       <c r="R8" t="n">
-        <v>7089631</v>
+        <v>7089685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121597807</v>
+        <v>121597834</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456131</v>
+        <v>456027</v>
       </c>
       <c r="R9" t="n">
-        <v>7089685</v>
+        <v>7089731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121597831</v>
+        <v>121597822</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455932</v>
+        <v>455878</v>
       </c>
       <c r="R10" t="n">
-        <v>7089722</v>
+        <v>7089626</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121597843</v>
+        <v>121597817</v>
       </c>
       <c r="B11" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,20 +1650,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1671,33 +1671,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455872</v>
+        <v>455940</v>
       </c>
       <c r="R11" t="n">
-        <v>7089681</v>
+        <v>7089592</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,6 +1714,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121597808</v>
+        <v>121597839</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1796,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456004</v>
+        <v>456158</v>
       </c>
       <c r="R12" t="n">
-        <v>7089704</v>
+        <v>7090028</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121597823</v>
+        <v>121597832</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1903,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455862</v>
+        <v>455959</v>
       </c>
       <c r="R13" t="n">
-        <v>7089621</v>
+        <v>7089716</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121597833</v>
+        <v>121597843</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,20 +1971,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2003,17 +1992,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456021</v>
+        <v>455872</v>
       </c>
       <c r="R14" t="n">
-        <v>7089738</v>
+        <v>7089681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,11 +2051,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,7 +2077,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121597829</v>
+        <v>121597810</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455874</v>
+        <v>456012</v>
       </c>
       <c r="R15" t="n">
-        <v>7089674</v>
+        <v>7089631</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,7 +2184,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597819</v>
+        <v>121597814</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455921</v>
+        <v>455985</v>
       </c>
       <c r="R16" t="n">
-        <v>7089667</v>
+        <v>7089602</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,7 +2291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121597818</v>
+        <v>121597815</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455942</v>
+        <v>455981</v>
       </c>
       <c r="R17" t="n">
-        <v>7089594</v>
+        <v>7089604</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,7 +2398,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121597834</v>
+        <v>121597838</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456027</v>
+        <v>456161</v>
       </c>
       <c r="R18" t="n">
-        <v>7089731</v>
+        <v>7090000</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,7 +2505,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121597825</v>
+        <v>121597811</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455860</v>
+        <v>455994</v>
       </c>
       <c r="R19" t="n">
-        <v>7089638</v>
+        <v>7089624</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,7 +2612,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121597809</v>
+        <v>121597819</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456010</v>
+        <v>455921</v>
       </c>
       <c r="R20" t="n">
-        <v>7089636</v>
+        <v>7089667</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,7 +2826,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121597814</v>
+        <v>121597821</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455985</v>
+        <v>455920</v>
       </c>
       <c r="R22" t="n">
-        <v>7089602</v>
+        <v>7089644</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2933,7 +2933,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121597813</v>
+        <v>121597828</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455988</v>
+        <v>455870</v>
       </c>
       <c r="R23" t="n">
-        <v>7089586</v>
+        <v>7089664</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121597830</v>
+        <v>121597820</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455863</v>
+        <v>455932</v>
       </c>
       <c r="R24" t="n">
-        <v>7089690</v>
+        <v>7089647</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3147,7 +3147,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121597820</v>
+        <v>121597831</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3190,7 +3190,7 @@
         <v>455932</v>
       </c>
       <c r="R25" t="n">
-        <v>7089647</v>
+        <v>7089722</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121597824</v>
+        <v>121597805</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455866</v>
+        <v>456204</v>
       </c>
       <c r="R26" t="n">
-        <v>7089627</v>
+        <v>7089607</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3361,7 +3361,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121597815</v>
+        <v>121597823</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455981</v>
+        <v>455862</v>
       </c>
       <c r="R27" t="n">
-        <v>7089604</v>
+        <v>7089621</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121597827</v>
+        <v>121597803</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455876</v>
+        <v>456311</v>
       </c>
       <c r="R28" t="n">
-        <v>7089661</v>
+        <v>7089646</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3575,7 +3575,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597817</v>
+        <v>121597833</v>
       </c>
       <c r="B29" t="n">
         <v>57356</v>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455940</v>
+        <v>456021</v>
       </c>
       <c r="R29" t="n">
-        <v>7089592</v>
+        <v>7089738</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121597805</v>
+        <v>121597813</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456204</v>
+        <v>455988</v>
       </c>
       <c r="R30" t="n">
-        <v>7089607</v>
+        <v>7089586</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3789,7 +3789,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121597811</v>
+        <v>121597802</v>
       </c>
       <c r="B31" t="n">
         <v>57356</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455994</v>
+        <v>456310</v>
       </c>
       <c r="R31" t="n">
-        <v>7089624</v>
+        <v>7089654</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3896,7 +3896,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121597802</v>
+        <v>121597808</v>
       </c>
       <c r="B32" t="n">
         <v>57356</v>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456310</v>
+        <v>456004</v>
       </c>
       <c r="R32" t="n">
-        <v>7089654</v>
+        <v>7089704</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4003,7 +4003,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597826</v>
+        <v>121597830</v>
       </c>
       <c r="B33" t="n">
         <v>57356</v>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455858</v>
+        <v>455863</v>
       </c>
       <c r="R33" t="n">
-        <v>7089658</v>
+        <v>7089690</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4110,7 +4110,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597839</v>
+        <v>121597825</v>
       </c>
       <c r="B34" t="n">
         <v>57356</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456158</v>
+        <v>455860</v>
       </c>
       <c r="R34" t="n">
-        <v>7090028</v>
+        <v>7089638</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4217,7 +4217,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597816</v>
+        <v>121597836</v>
       </c>
       <c r="B35" t="n">
         <v>57356</v>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455928</v>
+        <v>456036</v>
       </c>
       <c r="R35" t="n">
-        <v>7089592</v>
+        <v>7089837</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597836</v>
+        <v>121597835</v>
       </c>
       <c r="B36" t="n">
         <v>57356</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456036</v>
+        <v>456030</v>
       </c>
       <c r="R36" t="n">
-        <v>7089837</v>
+        <v>7089739</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4431,7 +4431,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597803</v>
+        <v>121597816</v>
       </c>
       <c r="B37" t="n">
         <v>57356</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456311</v>
+        <v>455928</v>
       </c>
       <c r="R37" t="n">
-        <v>7089646</v>
+        <v>7089592</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4538,7 +4538,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121597838</v>
+        <v>121597818</v>
       </c>
       <c r="B38" t="n">
         <v>57356</v>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456161</v>
+        <v>455942</v>
       </c>
       <c r="R38" t="n">
-        <v>7090000</v>
+        <v>7089594</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 49213-2024 artfynd.xlsx
+++ b/artfynd/A 49213-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597826</v>
+        <v>121597837</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455858</v>
+        <v>456058</v>
       </c>
       <c r="R2" t="n">
-        <v>7089658</v>
+        <v>7089872</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597837</v>
+        <v>121597826</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456058</v>
+        <v>455858</v>
       </c>
       <c r="R3" t="n">
-        <v>7089872</v>
+        <v>7089658</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49213-2024 artfynd.xlsx
+++ b/artfynd/A 49213-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597837</v>
+        <v>121597813</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456058</v>
+        <v>455988</v>
       </c>
       <c r="R2" t="n">
-        <v>7089872</v>
+        <v>7089586</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597826</v>
+        <v>121597803</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455858</v>
+        <v>456311</v>
       </c>
       <c r="R3" t="n">
-        <v>7089658</v>
+        <v>7089646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121597827</v>
+        <v>121597802</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455876</v>
+        <v>456310</v>
       </c>
       <c r="R4" t="n">
-        <v>7089661</v>
+        <v>7089654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121597829</v>
+        <v>121597826</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455874</v>
+        <v>455858</v>
       </c>
       <c r="R5" t="n">
-        <v>7089674</v>
+        <v>7089658</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121597809</v>
+        <v>121597816</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456010</v>
+        <v>455928</v>
       </c>
       <c r="R6" t="n">
-        <v>7089636</v>
+        <v>7089592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121597824</v>
+        <v>121597819</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455866</v>
+        <v>455921</v>
       </c>
       <c r="R7" t="n">
-        <v>7089627</v>
+        <v>7089667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597807</v>
+        <v>121597805</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456131</v>
+        <v>456204</v>
       </c>
       <c r="R8" t="n">
-        <v>7089685</v>
+        <v>7089607</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121597834</v>
+        <v>121597835</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456027</v>
+        <v>456030</v>
       </c>
       <c r="R9" t="n">
-        <v>7089731</v>
+        <v>7089739</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121597822</v>
+        <v>121597812</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455878</v>
+        <v>456010</v>
       </c>
       <c r="R10" t="n">
-        <v>7089626</v>
+        <v>7089564</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121597817</v>
+        <v>121597818</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455940</v>
+        <v>455942</v>
       </c>
       <c r="R11" t="n">
-        <v>7089592</v>
+        <v>7089594</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121597839</v>
+        <v>121597817</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456158</v>
+        <v>455940</v>
       </c>
       <c r="R12" t="n">
-        <v>7090028</v>
+        <v>7089592</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121597832</v>
+        <v>121597823</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455959</v>
+        <v>455862</v>
       </c>
       <c r="R13" t="n">
-        <v>7089716</v>
+        <v>7089621</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121597843</v>
+        <v>121597814</v>
       </c>
       <c r="B14" t="n">
-        <v>57467</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1971,20 +1971,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1992,33 +1992,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455872</v>
+        <v>455985</v>
       </c>
       <c r="R14" t="n">
-        <v>7089681</v>
+        <v>7089602</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,6 +2035,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121597810</v>
+        <v>121597822</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2117,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456012</v>
+        <v>455878</v>
       </c>
       <c r="R15" t="n">
-        <v>7089631</v>
+        <v>7089626</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597814</v>
+        <v>121597827</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2224,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455985</v>
+        <v>455876</v>
       </c>
       <c r="R16" t="n">
-        <v>7089602</v>
+        <v>7089661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121597815</v>
+        <v>121597825</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2331,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455981</v>
+        <v>455860</v>
       </c>
       <c r="R17" t="n">
-        <v>7089604</v>
+        <v>7089638</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121597838</v>
+        <v>121597829</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2438,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456161</v>
+        <v>455874</v>
       </c>
       <c r="R18" t="n">
-        <v>7090000</v>
+        <v>7089674</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121597811</v>
+        <v>121597815</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2545,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455994</v>
+        <v>455981</v>
       </c>
       <c r="R19" t="n">
-        <v>7089624</v>
+        <v>7089604</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2585,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121597819</v>
+        <v>121597831</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2652,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455921</v>
+        <v>455932</v>
       </c>
       <c r="R20" t="n">
-        <v>7089667</v>
+        <v>7089722</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2719,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121597812</v>
+        <v>121597836</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2759,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456010</v>
+        <v>456036</v>
       </c>
       <c r="R21" t="n">
-        <v>7089564</v>
+        <v>7089837</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2788,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2826,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121597821</v>
+        <v>121597807</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2866,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455920</v>
+        <v>456131</v>
       </c>
       <c r="R22" t="n">
-        <v>7089644</v>
+        <v>7089685</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2895,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2933,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121597828</v>
+        <v>121597837</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2973,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455870</v>
+        <v>456058</v>
       </c>
       <c r="R23" t="n">
-        <v>7089664</v>
+        <v>7089872</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3040,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121597820</v>
+        <v>121597824</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3080,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455932</v>
+        <v>455866</v>
       </c>
       <c r="R24" t="n">
-        <v>7089647</v>
+        <v>7089627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121597831</v>
+        <v>121597839</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3187,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455932</v>
+        <v>456158</v>
       </c>
       <c r="R25" t="n">
-        <v>7089722</v>
+        <v>7090028</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,7 +3216,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121597805</v>
+        <v>121597809</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3294,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456204</v>
+        <v>456010</v>
       </c>
       <c r="R26" t="n">
-        <v>7089607</v>
+        <v>7089636</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,7 +3323,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3361,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121597823</v>
+        <v>121597811</v>
       </c>
       <c r="B27" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3401,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455862</v>
+        <v>455994</v>
       </c>
       <c r="R27" t="n">
-        <v>7089621</v>
+        <v>7089624</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,7 +3430,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121597803</v>
+        <v>121597821</v>
       </c>
       <c r="B28" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3508,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456311</v>
+        <v>455920</v>
       </c>
       <c r="R28" t="n">
-        <v>7089646</v>
+        <v>7089644</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597833</v>
+        <v>121597843</v>
       </c>
       <c r="B29" t="n">
-        <v>57356</v>
+        <v>57468</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3587,20 +3576,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3608,17 +3597,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456021</v>
+        <v>455872</v>
       </c>
       <c r="R29" t="n">
-        <v>7089738</v>
+        <v>7089681</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,11 +3656,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3682,10 +3682,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121597813</v>
+        <v>121597828</v>
       </c>
       <c r="B30" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455988</v>
+        <v>455870</v>
       </c>
       <c r="R30" t="n">
-        <v>7089586</v>
+        <v>7089664</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121597802</v>
+        <v>121597832</v>
       </c>
       <c r="B31" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456310</v>
+        <v>455959</v>
       </c>
       <c r="R31" t="n">
-        <v>7089654</v>
+        <v>7089716</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3899,7 +3899,7 @@
         <v>121597808</v>
       </c>
       <c r="B32" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4003,10 +4003,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597830</v>
+        <v>121597833</v>
       </c>
       <c r="B33" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455863</v>
+        <v>456021</v>
       </c>
       <c r="R33" t="n">
-        <v>7089690</v>
+        <v>7089738</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4110,10 +4110,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597825</v>
+        <v>121597834</v>
       </c>
       <c r="B34" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455860</v>
+        <v>456027</v>
       </c>
       <c r="R34" t="n">
-        <v>7089638</v>
+        <v>7089731</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4217,10 +4217,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597836</v>
+        <v>121597810</v>
       </c>
       <c r="B35" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456036</v>
+        <v>456012</v>
       </c>
       <c r="R35" t="n">
-        <v>7089837</v>
+        <v>7089631</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,10 +4324,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597835</v>
+        <v>121597820</v>
       </c>
       <c r="B36" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456030</v>
+        <v>455932</v>
       </c>
       <c r="R36" t="n">
-        <v>7089739</v>
+        <v>7089647</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,10 +4431,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597816</v>
+        <v>121597830</v>
       </c>
       <c r="B37" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455928</v>
+        <v>455863</v>
       </c>
       <c r="R37" t="n">
-        <v>7089592</v>
+        <v>7089690</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4538,10 +4538,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121597818</v>
+        <v>121597838</v>
       </c>
       <c r="B38" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455942</v>
+        <v>456161</v>
       </c>
       <c r="R38" t="n">
-        <v>7089594</v>
+        <v>7090000</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 49213-2024 artfynd.xlsx
+++ b/artfynd/A 49213-2024 artfynd.xlsx
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121597836</v>
+        <v>121597824</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456036</v>
+        <v>455866</v>
       </c>
       <c r="R21" t="n">
-        <v>7089837</v>
+        <v>7089627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121597807</v>
+        <v>121597836</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456131</v>
+        <v>456036</v>
       </c>
       <c r="R22" t="n">
-        <v>7089685</v>
+        <v>7089837</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121597837</v>
+        <v>121597807</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456058</v>
+        <v>456131</v>
       </c>
       <c r="R23" t="n">
-        <v>7089872</v>
+        <v>7089685</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,7 +3029,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121597824</v>
+        <v>121597837</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455866</v>
+        <v>456058</v>
       </c>
       <c r="R24" t="n">
-        <v>7089627</v>
+        <v>7089872</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 49213-2024 artfynd.xlsx
+++ b/artfynd/A 49213-2024 artfynd.xlsx
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121597824</v>
+        <v>121597836</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455866</v>
+        <v>456036</v>
       </c>
       <c r="R21" t="n">
-        <v>7089627</v>
+        <v>7089837</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121597836</v>
+        <v>121597807</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456036</v>
+        <v>456131</v>
       </c>
       <c r="R22" t="n">
-        <v>7089837</v>
+        <v>7089685</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121597807</v>
+        <v>121597837</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456131</v>
+        <v>456058</v>
       </c>
       <c r="R23" t="n">
-        <v>7089685</v>
+        <v>7089872</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,7 +3029,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121597837</v>
+        <v>121597824</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456058</v>
+        <v>455866</v>
       </c>
       <c r="R24" t="n">
-        <v>7089872</v>
+        <v>7089627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 49213-2024 artfynd.xlsx
+++ b/artfynd/A 49213-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597819</v>
+        <v>121597809</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455921</v>
+        <v>456010</v>
       </c>
       <c r="R2" t="n">
-        <v>7089667</v>
+        <v>7089636</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597818</v>
+        <v>121597810</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455942</v>
+        <v>456012</v>
       </c>
       <c r="R3" t="n">
-        <v>7089594</v>
+        <v>7089631</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121597820</v>
+        <v>121597843</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,20 +901,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -922,17 +922,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455932</v>
+        <v>455872</v>
       </c>
       <c r="R4" t="n">
-        <v>7089647</v>
+        <v>7089681</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +981,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121597827</v>
+        <v>121597817</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455876</v>
+        <v>455940</v>
       </c>
       <c r="R5" t="n">
-        <v>7089661</v>
+        <v>7089592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1087,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121597825</v>
+        <v>121597826</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455860</v>
+        <v>455858</v>
       </c>
       <c r="R6" t="n">
-        <v>7089638</v>
+        <v>7089658</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121597808</v>
+        <v>121597836</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1250,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456004</v>
+        <v>456036</v>
       </c>
       <c r="R7" t="n">
-        <v>7089704</v>
+        <v>7089837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1301,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1328,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597833</v>
+        <v>121597807</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1357,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456021</v>
+        <v>456131</v>
       </c>
       <c r="R8" t="n">
-        <v>7089738</v>
+        <v>7089685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1408,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121597802</v>
+        <v>121597803</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1464,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456310</v>
+        <v>456311</v>
       </c>
       <c r="R9" t="n">
-        <v>7089654</v>
+        <v>7089646</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1542,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121597805</v>
+        <v>121597837</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1571,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456204</v>
+        <v>456058</v>
       </c>
       <c r="R10" t="n">
-        <v>7089607</v>
+        <v>7089872</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121597816</v>
+        <v>121597825</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1678,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455928</v>
+        <v>455860</v>
       </c>
       <c r="R11" t="n">
-        <v>7089592</v>
+        <v>7089638</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1729,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121597822</v>
+        <v>121597819</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1785,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455878</v>
+        <v>455921</v>
       </c>
       <c r="R12" t="n">
-        <v>7089626</v>
+        <v>7089667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121597832</v>
+        <v>121597830</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1892,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455959</v>
+        <v>455863</v>
       </c>
       <c r="R13" t="n">
-        <v>7089716</v>
+        <v>7089690</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1943,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1970,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121597817</v>
+        <v>121597838</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -1999,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455940</v>
+        <v>456161</v>
       </c>
       <c r="R14" t="n">
-        <v>7089592</v>
+        <v>7090000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2077,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121597838</v>
+        <v>121597805</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2106,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456161</v>
+        <v>456204</v>
       </c>
       <c r="R15" t="n">
-        <v>7090000</v>
+        <v>7089607</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2157,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2184,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597810</v>
+        <v>121597829</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2213,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456012</v>
+        <v>455874</v>
       </c>
       <c r="R16" t="n">
-        <v>7089631</v>
+        <v>7089674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2264,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121597828</v>
+        <v>121597835</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2320,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455870</v>
+        <v>456030</v>
       </c>
       <c r="R17" t="n">
-        <v>7089664</v>
+        <v>7089739</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2371,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121597843</v>
+        <v>121597827</v>
       </c>
       <c r="B18" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2399,20 +2410,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2420,33 +2431,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455872</v>
+        <v>455876</v>
       </c>
       <c r="R18" t="n">
-        <v>7089681</v>
+        <v>7089661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,6 +2474,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,7 +2505,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121597824</v>
+        <v>121597812</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455866</v>
+        <v>456010</v>
       </c>
       <c r="R19" t="n">
-        <v>7089627</v>
+        <v>7089564</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,7 +2612,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121597821</v>
+        <v>121597824</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455920</v>
+        <v>455866</v>
       </c>
       <c r="R20" t="n">
-        <v>7089644</v>
+        <v>7089627</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121597812</v>
+        <v>121597811</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456010</v>
+        <v>455994</v>
       </c>
       <c r="R21" t="n">
-        <v>7089564</v>
+        <v>7089624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2826,7 +2826,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121597835</v>
+        <v>121597808</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456030</v>
+        <v>456004</v>
       </c>
       <c r="R22" t="n">
-        <v>7089739</v>
+        <v>7089704</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2933,7 +2933,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121597831</v>
+        <v>121597813</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455932</v>
+        <v>455988</v>
       </c>
       <c r="R23" t="n">
-        <v>7089722</v>
+        <v>7089586</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3040,7 +3040,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121597823</v>
+        <v>121597822</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455862</v>
+        <v>455878</v>
       </c>
       <c r="R24" t="n">
-        <v>7089621</v>
+        <v>7089626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,7 +3147,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121597811</v>
+        <v>121597832</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455994</v>
+        <v>455959</v>
       </c>
       <c r="R25" t="n">
-        <v>7089624</v>
+        <v>7089716</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,7 +3254,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121597803</v>
+        <v>121597818</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456311</v>
+        <v>455942</v>
       </c>
       <c r="R26" t="n">
-        <v>7089646</v>
+        <v>7089594</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3361,7 +3361,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121597830</v>
+        <v>121597814</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455863</v>
+        <v>455985</v>
       </c>
       <c r="R27" t="n">
-        <v>7089690</v>
+        <v>7089602</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,7 +3468,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121597814</v>
+        <v>121597823</v>
       </c>
       <c r="B28" t="n">
         <v>57357</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455985</v>
+        <v>455862</v>
       </c>
       <c r="R28" t="n">
-        <v>7089602</v>
+        <v>7089621</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597836</v>
+        <v>121597833</v>
       </c>
       <c r="B29" t="n">
         <v>57357</v>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456036</v>
+        <v>456021</v>
       </c>
       <c r="R29" t="n">
-        <v>7089837</v>
+        <v>7089738</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3682,7 +3682,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121597807</v>
+        <v>121597839</v>
       </c>
       <c r="B30" t="n">
         <v>57357</v>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456131</v>
+        <v>456158</v>
       </c>
       <c r="R30" t="n">
-        <v>7089685</v>
+        <v>7090028</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3789,7 +3789,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121597837</v>
+        <v>121597820</v>
       </c>
       <c r="B31" t="n">
         <v>57357</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456058</v>
+        <v>455932</v>
       </c>
       <c r="R31" t="n">
-        <v>7089872</v>
+        <v>7089647</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3896,7 +3896,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121597834</v>
+        <v>121597828</v>
       </c>
       <c r="B32" t="n">
         <v>57357</v>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456027</v>
+        <v>455870</v>
       </c>
       <c r="R32" t="n">
-        <v>7089731</v>
+        <v>7089664</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4003,7 +4003,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597815</v>
+        <v>121597802</v>
       </c>
       <c r="B33" t="n">
         <v>57357</v>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455981</v>
+        <v>456310</v>
       </c>
       <c r="R33" t="n">
-        <v>7089604</v>
+        <v>7089654</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597829</v>
+        <v>121597816</v>
       </c>
       <c r="B34" t="n">
         <v>57357</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455874</v>
+        <v>455928</v>
       </c>
       <c r="R34" t="n">
-        <v>7089674</v>
+        <v>7089592</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4217,7 +4217,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597839</v>
+        <v>121597815</v>
       </c>
       <c r="B35" t="n">
         <v>57357</v>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456158</v>
+        <v>455981</v>
       </c>
       <c r="R35" t="n">
-        <v>7090028</v>
+        <v>7089604</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,7 +4324,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597826</v>
+        <v>121597831</v>
       </c>
       <c r="B36" t="n">
         <v>57357</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455858</v>
+        <v>455932</v>
       </c>
       <c r="R36" t="n">
-        <v>7089658</v>
+        <v>7089722</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4431,7 +4431,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597809</v>
+        <v>121597834</v>
       </c>
       <c r="B37" t="n">
         <v>57357</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456010</v>
+        <v>456027</v>
       </c>
       <c r="R37" t="n">
-        <v>7089636</v>
+        <v>7089731</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4538,7 +4538,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121597813</v>
+        <v>121597821</v>
       </c>
       <c r="B38" t="n">
         <v>57357</v>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455988</v>
+        <v>455920</v>
       </c>
       <c r="R38" t="n">
-        <v>7089586</v>
+        <v>7089644</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 49213-2024 artfynd.xlsx
+++ b/artfynd/A 49213-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597809</v>
+        <v>121597824</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456010</v>
+        <v>455866</v>
       </c>
       <c r="R2" t="n">
-        <v>7089636</v>
+        <v>7089627</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597810</v>
+        <v>121597836</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456012</v>
+        <v>456036</v>
       </c>
       <c r="R3" t="n">
-        <v>7089631</v>
+        <v>7089837</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121597843</v>
+        <v>121597825</v>
       </c>
       <c r="B4" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,20 +901,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -922,33 +922,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455872</v>
+        <v>455860</v>
       </c>
       <c r="R4" t="n">
-        <v>7089681</v>
+        <v>7089638</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121597817</v>
+        <v>121597830</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1047,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455940</v>
+        <v>455863</v>
       </c>
       <c r="R5" t="n">
-        <v>7089592</v>
+        <v>7089690</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121597826</v>
+        <v>121597835</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1154,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455858</v>
+        <v>456030</v>
       </c>
       <c r="R6" t="n">
-        <v>7089658</v>
+        <v>7089739</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121597836</v>
+        <v>121597817</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1261,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456036</v>
+        <v>455940</v>
       </c>
       <c r="R7" t="n">
-        <v>7089837</v>
+        <v>7089592</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597807</v>
+        <v>121597843</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,20 +1329,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1361,17 +1350,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456131</v>
+        <v>455872</v>
       </c>
       <c r="R8" t="n">
-        <v>7089685</v>
+        <v>7089681</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,11 +1409,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121597803</v>
+        <v>121597831</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456311</v>
+        <v>455932</v>
       </c>
       <c r="R9" t="n">
-        <v>7089646</v>
+        <v>7089722</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121597837</v>
+        <v>121597838</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456058</v>
+        <v>456161</v>
       </c>
       <c r="R10" t="n">
-        <v>7089872</v>
+        <v>7090000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121597825</v>
+        <v>121597833</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455860</v>
+        <v>456021</v>
       </c>
       <c r="R11" t="n">
-        <v>7089638</v>
+        <v>7089738</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121597819</v>
+        <v>121597809</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455921</v>
+        <v>456010</v>
       </c>
       <c r="R12" t="n">
-        <v>7089667</v>
+        <v>7089636</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121597830</v>
+        <v>121597811</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455863</v>
+        <v>455994</v>
       </c>
       <c r="R13" t="n">
-        <v>7089690</v>
+        <v>7089624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,7 +1970,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121597838</v>
+        <v>121597822</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456161</v>
+        <v>455878</v>
       </c>
       <c r="R14" t="n">
-        <v>7090000</v>
+        <v>7089626</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2077,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121597805</v>
+        <v>121597812</v>
       </c>
       <c r="B15" t="n">
         <v>57357</v>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456204</v>
+        <v>456010</v>
       </c>
       <c r="R15" t="n">
-        <v>7089607</v>
+        <v>7089564</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,7 +2184,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121597829</v>
+        <v>121597813</v>
       </c>
       <c r="B16" t="n">
         <v>57357</v>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455874</v>
+        <v>455988</v>
       </c>
       <c r="R16" t="n">
-        <v>7089674</v>
+        <v>7089586</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,7 +2291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121597835</v>
+        <v>121597837</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456030</v>
+        <v>456058</v>
       </c>
       <c r="R17" t="n">
-        <v>7089739</v>
+        <v>7089872</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,7 +2398,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121597827</v>
+        <v>121597819</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455876</v>
+        <v>455921</v>
       </c>
       <c r="R18" t="n">
-        <v>7089661</v>
+        <v>7089667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121597812</v>
+        <v>121597810</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456010</v>
+        <v>456012</v>
       </c>
       <c r="R19" t="n">
-        <v>7089564</v>
+        <v>7089631</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,7 +2612,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121597824</v>
+        <v>121597834</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455866</v>
+        <v>456027</v>
       </c>
       <c r="R20" t="n">
-        <v>7089627</v>
+        <v>7089731</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2719,7 +2719,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121597811</v>
+        <v>121597826</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455994</v>
+        <v>455858</v>
       </c>
       <c r="R21" t="n">
-        <v>7089624</v>
+        <v>7089658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2826,7 +2826,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121597808</v>
+        <v>121597818</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456004</v>
+        <v>455942</v>
       </c>
       <c r="R22" t="n">
-        <v>7089704</v>
+        <v>7089594</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2933,7 +2933,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121597813</v>
+        <v>121597823</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455988</v>
+        <v>455862</v>
       </c>
       <c r="R23" t="n">
-        <v>7089586</v>
+        <v>7089621</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3040,7 +3040,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121597822</v>
+        <v>121597827</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455878</v>
+        <v>455876</v>
       </c>
       <c r="R24" t="n">
-        <v>7089626</v>
+        <v>7089661</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3147,7 +3147,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121597832</v>
+        <v>121597805</v>
       </c>
       <c r="B25" t="n">
         <v>57357</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455959</v>
+        <v>456204</v>
       </c>
       <c r="R25" t="n">
-        <v>7089716</v>
+        <v>7089607</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,7 +3254,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121597818</v>
+        <v>121597816</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455942</v>
+        <v>455928</v>
       </c>
       <c r="R26" t="n">
-        <v>7089594</v>
+        <v>7089592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121597814</v>
+        <v>121597807</v>
       </c>
       <c r="B27" t="n">
         <v>57357</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455985</v>
+        <v>456131</v>
       </c>
       <c r="R27" t="n">
-        <v>7089602</v>
+        <v>7089685</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,7 +3468,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121597823</v>
+        <v>121597829</v>
       </c>
       <c r="B28" t="n">
         <v>57357</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455862</v>
+        <v>455874</v>
       </c>
       <c r="R28" t="n">
-        <v>7089621</v>
+        <v>7089674</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3575,7 +3575,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121597833</v>
+        <v>121597815</v>
       </c>
       <c r="B29" t="n">
         <v>57357</v>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456021</v>
+        <v>455981</v>
       </c>
       <c r="R29" t="n">
-        <v>7089738</v>
+        <v>7089604</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3789,7 +3789,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121597820</v>
+        <v>121597821</v>
       </c>
       <c r="B31" t="n">
         <v>57357</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455932</v>
+        <v>455920</v>
       </c>
       <c r="R31" t="n">
-        <v>7089647</v>
+        <v>7089644</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121597828</v>
+        <v>121597808</v>
       </c>
       <c r="B32" t="n">
         <v>57357</v>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455870</v>
+        <v>456004</v>
       </c>
       <c r="R32" t="n">
-        <v>7089664</v>
+        <v>7089704</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4003,7 +4003,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121597802</v>
+        <v>121597828</v>
       </c>
       <c r="B33" t="n">
         <v>57357</v>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456310</v>
+        <v>455870</v>
       </c>
       <c r="R33" t="n">
-        <v>7089654</v>
+        <v>7089664</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4110,7 +4110,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121597816</v>
+        <v>121597814</v>
       </c>
       <c r="B34" t="n">
         <v>57357</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455928</v>
+        <v>455985</v>
       </c>
       <c r="R34" t="n">
-        <v>7089592</v>
+        <v>7089602</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4217,7 +4217,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121597815</v>
+        <v>121597832</v>
       </c>
       <c r="B35" t="n">
         <v>57357</v>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455981</v>
+        <v>455959</v>
       </c>
       <c r="R35" t="n">
-        <v>7089604</v>
+        <v>7089716</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,7 +4324,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121597831</v>
+        <v>121597803</v>
       </c>
       <c r="B36" t="n">
         <v>57357</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455932</v>
+        <v>456311</v>
       </c>
       <c r="R36" t="n">
-        <v>7089722</v>
+        <v>7089646</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121597834</v>
+        <v>121597820</v>
       </c>
       <c r="B37" t="n">
         <v>57357</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456027</v>
+        <v>455932</v>
       </c>
       <c r="R37" t="n">
-        <v>7089731</v>
+        <v>7089647</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4538,7 +4538,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121597821</v>
+        <v>121597802</v>
       </c>
       <c r="B38" t="n">
         <v>57357</v>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455920</v>
+        <v>456310</v>
       </c>
       <c r="R38" t="n">
-        <v>7089644</v>
+        <v>7089654</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
